--- a/public/exports-60-250-with-coowners/29188548.xlsx
+++ b/public/exports-60-250-with-coowners/29188548.xlsx
@@ -2441,40 +2441,40 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 35</t>
+          <t xml:space="preserve">Kirsebærhaven 12</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070</t>
+          <t xml:space="preserve">4330</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2224218</t>
+          <t xml:space="preserve">2222525</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J33">
-        <v>62</v>
+        <v>180</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253139</t>
+          <t xml:space="preserve">311255463</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-12</t>
+          <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirsebærhaven 12</t>
+          <t xml:space="preserve">Kirsebærhaven 18</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2531,11 +2531,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J34">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirsebærhaven 18</t>
+          <t xml:space="preserve">Kirsebærhaven 2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J35">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirsebærhaven 2</t>
+          <t xml:space="preserve">Kirsebærhaven 26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2681,11 +2681,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J36">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirsebærhaven 26</t>
+          <t xml:space="preserve">Tolstrupvej 30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2751,20 +2751,20 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222525</t>
+          <t xml:space="preserve">2232068</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J37">
-        <v>200</v>
+        <v>142</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255463</t>
+          <t xml:space="preserve">311255467</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2816,17 +2816,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tolstrupvej 30</t>
+          <t xml:space="preserve">Gershøjvej 111</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4330</t>
+          <t xml:space="preserve">4070</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2232068</t>
+          <t xml:space="preserve">2221130</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2835,21 +2835,21 @@
         </is>
       </c>
       <c r="J38">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255467</t>
+          <t xml:space="preserve">311256397</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-21</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gershøjvej 111</t>
+          <t xml:space="preserve">Grønager 2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2221130</t>
+          <t xml:space="preserve">2221510</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2910,16 +2910,16 @@
         </is>
       </c>
       <c r="J39">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256397</t>
+          <t xml:space="preserve">311256384</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønager 2</t>
+          <t xml:space="preserve">Bognæsvej 11A</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2976,20 +2976,20 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2221510</t>
+          <t xml:space="preserve">2172366</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J40">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256384</t>
+          <t xml:space="preserve">311256753</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-06-27</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bognæsvej 11A</t>
+          <t xml:space="preserve">Bognæsvej 11C</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J41">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bognæsvej 11C</t>
+          <t xml:space="preserve">Bognæsvej 11E</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J42">
@@ -3191,30 +3191,30 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bognæsvej 11E</t>
+          <t xml:space="preserve">Byvejen 35A</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4320</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172366</t>
+          <t xml:space="preserve">2227064</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J43">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256753</t>
+          <t xml:space="preserve">311256747</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3266,17 +3266,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvejen 35A</t>
+          <t xml:space="preserve">Hornsherredvej 437</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320</t>
+          <t xml:space="preserve">4070</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2227064</t>
+          <t xml:space="preserve">2231992</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3285,16 +3285,16 @@
         </is>
       </c>
       <c r="J44">
-        <v>131</v>
+        <v>180</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256747</t>
+          <t xml:space="preserve">311256729</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hornsherredvej 437</t>
+          <t xml:space="preserve">Karlebyvej 54A</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2231992</t>
+          <t xml:space="preserve">2225586</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3360,16 +3360,16 @@
         </is>
       </c>
       <c r="J45">
-        <v>180</v>
+        <v>123</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256729</t>
+          <t xml:space="preserve">311256725</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karlebyvej 54A</t>
+          <t xml:space="preserve">Karlebyvej 54C</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2225586</t>
+          <t xml:space="preserve">2225587</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3435,11 +3435,11 @@
         </is>
       </c>
       <c r="J46">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256725</t>
+          <t xml:space="preserve">311256727</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3491,17 +3491,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karlebyvej 54C</t>
+          <t xml:space="preserve">Langetoften 17</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070</t>
+          <t xml:space="preserve">4320</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2225587</t>
+          <t xml:space="preserve">2226625</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3510,11 +3510,11 @@
         </is>
       </c>
       <c r="J47">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256727</t>
+          <t xml:space="preserve">311256732</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3566,40 +3566,40 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 17</t>
+          <t xml:space="preserve">Kirsebærhaven 15</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320</t>
+          <t xml:space="preserve">4330</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2226625</t>
+          <t xml:space="preserve">2222525</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J48">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256732</t>
+          <t xml:space="preserve">311257068</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-27</t>
+          <t xml:space="preserve">2027-06-28</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirsebærhaven 15</t>
+          <t xml:space="preserve">Kirsebærhaven 19</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J49">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirsebærhaven 19</t>
+          <t xml:space="preserve">Kirsebærhaven 23</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J50">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirsebærhaven 23</t>
+          <t xml:space="preserve">Kirsebærhaven 3</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J51">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirsebærhaven 3</t>
+          <t xml:space="preserve">Kirsebærhaven 32</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J52">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirsebærhaven 32</t>
+          <t xml:space="preserve">Kirsebærhaven 7</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J53">
@@ -4016,40 +4016,40 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirsebærhaven 7</t>
+          <t xml:space="preserve">Bygmarken 78</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4330</t>
+          <t xml:space="preserve">4060</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222525</t>
+          <t xml:space="preserve">2231003</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J54">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257068</t>
+          <t xml:space="preserve">311258453</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-28</t>
+          <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygmarken 78</t>
+          <t xml:space="preserve">Langetoften 13A</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">4060</t>
+          <t xml:space="preserve">4320</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2231003</t>
+          <t xml:space="preserve">2226627</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4110,11 +4110,11 @@
         </is>
       </c>
       <c r="J55">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258453</t>
+          <t xml:space="preserve">311258486</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4166,17 +4166,17 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 13A</t>
+          <t xml:space="preserve">Engvej 5</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320</t>
+          <t xml:space="preserve">4070</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2226627</t>
+          <t xml:space="preserve">2226064</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4185,11 +4185,11 @@
         </is>
       </c>
       <c r="J56">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258486</t>
+          <t xml:space="preserve">311258899</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-03</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4241,17 +4241,17 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engvej 5</t>
+          <t xml:space="preserve">Langetoften 12A</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070</t>
+          <t xml:space="preserve">4320</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2226064</t>
+          <t xml:space="preserve">2226637</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4260,11 +4260,11 @@
         </is>
       </c>
       <c r="J57">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258899</t>
+          <t xml:space="preserve">311259010</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-07-05</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 12A</t>
+          <t xml:space="preserve">Oldvejen 2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2226637</t>
+          <t xml:space="preserve">9826008</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4335,11 +4335,11 @@
         </is>
       </c>
       <c r="J58">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259010</t>
+          <t xml:space="preserve">311259007</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4391,17 +4391,17 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oldvejen 2</t>
+          <t xml:space="preserve">Nordre Ryevej 52</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4060</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">9826008</t>
+          <t xml:space="preserve">2228828</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4410,11 +4410,11 @@
         </is>
       </c>
       <c r="J59">
-        <v>91</v>
+        <v>154</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259007</t>
+          <t xml:space="preserve">311264700</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-05</t>
+          <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4466,35 +4466,35 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Ryevej 52</t>
+          <t xml:space="preserve">Roskildevej 9B</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">4060</t>
+          <t xml:space="preserve">4330</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228828</t>
+          <t xml:space="preserve">2222449</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J60">
-        <v>154</v>
+        <v>66</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264700</t>
+          <t xml:space="preserve">311264717</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4556,11 +4556,11 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J61">
-        <v>66</v>
+        <v>141</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -4616,40 +4616,40 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskildevej 9B</t>
+          <t xml:space="preserve">Bygaden 28A</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4330</t>
+          <t xml:space="preserve">4070</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222449</t>
+          <t xml:space="preserve">2223861</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J62">
-        <v>141</v>
+        <v>250</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264717</t>
+          <t xml:space="preserve">311266807</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-07</t>
+          <t xml:space="preserve">2027-08-17</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4691,40 +4691,40 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 28A</t>
+          <t xml:space="preserve">Rynkebjerggårdsvej 61</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070</t>
+          <t xml:space="preserve">4320</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2223861</t>
+          <t xml:space="preserve">2218253</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J63">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311266807</t>
+          <t xml:space="preserve">311267861</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-17</t>
+          <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4766,40 +4766,40 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rynkebjerggårdsvej 61</t>
+          <t xml:space="preserve">Hyldebjerg 72</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320</t>
+          <t xml:space="preserve">4330</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2218253</t>
+          <t xml:space="preserve">9307053</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J64">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267861</t>
+          <t xml:space="preserve">311268972</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-22</t>
+          <t xml:space="preserve">2027-08-28</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4841,17 +4841,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyldebjerg 72</t>
+          <t xml:space="preserve">Fyrrevænget 8</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4330</t>
+          <t xml:space="preserve">4060</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">9307053</t>
+          <t xml:space="preserve">2229465</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4860,11 +4860,11 @@
         </is>
       </c>
       <c r="J65">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311268972</t>
+          <t xml:space="preserve">311271601</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-28</t>
+          <t xml:space="preserve">2027-09-07</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4916,17 +4916,17 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fyrrevænget 8</t>
+          <t xml:space="preserve">Sandbechs Alle 2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">4060</t>
+          <t xml:space="preserve">4330</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2229465</t>
+          <t xml:space="preserve">2222421</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4935,11 +4935,11 @@
         </is>
       </c>
       <c r="J66">
-        <v>220</v>
+        <v>101</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271601</t>
+          <t xml:space="preserve">311271574</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4991,40 +4991,40 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandbechs Alle 2</t>
+          <t xml:space="preserve">Langetoften 11A</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">4330</t>
+          <t xml:space="preserve">4320</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222421</t>
+          <t xml:space="preserve">2226614</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J67">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271574</t>
+          <t xml:space="preserve">311272660</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-07</t>
+          <t xml:space="preserve">2027-09-13</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 11A</t>
+          <t xml:space="preserve">Langetoften 11C</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J68">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 11C</t>
+          <t xml:space="preserve">Langetoften 11E</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5156,11 +5156,11 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J69">
-        <v>149</v>
+        <v>219</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 11E</t>
+          <t xml:space="preserve">Langetoften 11H</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J70">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 11H</t>
+          <t xml:space="preserve">Langetoften 11M</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5306,11 +5306,11 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J71">
-        <v>219</v>
+        <v>149</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 11M</t>
+          <t xml:space="preserve">Langetoften 7A</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5381,15 +5381,15 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J72">
-        <v>149</v>
+        <v>219</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272660</t>
+          <t xml:space="preserve">311272658</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 7A</t>
+          <t xml:space="preserve">Langetoften 7D</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5456,11 +5456,11 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J73">
-        <v>219</v>
+        <v>149</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 7D</t>
+          <t xml:space="preserve">Langetoften 7F</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J74">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 7F</t>
+          <t xml:space="preserve">Langetoften 7H</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J75">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 7H</t>
+          <t xml:space="preserve">Langetoften 7L</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5681,11 +5681,11 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J76">
-        <v>149</v>
+        <v>219</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 7L</t>
+          <t xml:space="preserve">Åbanken 22A</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5751,20 +5751,20 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2226614</t>
+          <t xml:space="preserve">7833238</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J77">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272658</t>
+          <t xml:space="preserve">311272654</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5816,30 +5816,30 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åbanken 22A</t>
+          <t xml:space="preserve">Skolevej 12</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320</t>
+          <t xml:space="preserve">4330</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">7833238</t>
+          <t xml:space="preserve">2222340</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J78">
-        <v>240</v>
+        <v>192</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272654</t>
+          <t xml:space="preserve">311275664</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-13</t>
+          <t xml:space="preserve">2027-09-28</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 12</t>
+          <t xml:space="preserve">Horseager 15</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222340</t>
+          <t xml:space="preserve">2222743, 100756340</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5910,11 +5910,11 @@
         </is>
       </c>
       <c r="J79">
-        <v>192</v>
+        <v>147</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275664</t>
+          <t xml:space="preserve">311276415</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-28</t>
+          <t xml:space="preserve">2027-10-03</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horseager 15</t>
+          <t xml:space="preserve">Horseager 15A</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5976,20 +5976,20 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222743, 100756340</t>
+          <t xml:space="preserve">2222743</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J80">
-        <v>147</v>
+        <v>198</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276415</t>
+          <t xml:space="preserve">311276416</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6041,40 +6041,40 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horseager 15A</t>
+          <t xml:space="preserve">Sonnerup Gade 4</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">4330</t>
+          <t xml:space="preserve">4060</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222743</t>
+          <t xml:space="preserve">2230776</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J81">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276416</t>
+          <t xml:space="preserve">311282473</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-03</t>
+          <t xml:space="preserve">2027-11-07</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6116,40 +6116,40 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sonnerup Gade 4</t>
+          <t xml:space="preserve">Herslevvej 23A</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">4060</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2230776</t>
+          <t xml:space="preserve">2172657</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J82">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282473</t>
+          <t xml:space="preserve">311285213</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-07</t>
+          <t xml:space="preserve">2027-11-22</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6206,11 +6206,11 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J83">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -6266,30 +6266,30 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herslevvej 23A</t>
+          <t xml:space="preserve">Bogøvej 11</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4060</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172657</t>
+          <t xml:space="preserve">2229495</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="J84">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285213</t>
+          <t xml:space="preserve">311291937</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-22</t>
+          <t xml:space="preserve">2028-01-10</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bogøvej 11</t>
+          <t xml:space="preserve">Bogøvej 13</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6351,20 +6351,20 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2229495</t>
+          <t xml:space="preserve">2229011</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J85">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291937</t>
+          <t xml:space="preserve">311291940</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6416,30 +6416,30 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bogøvej 13</t>
+          <t xml:space="preserve">Bygaden 49</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">4060</t>
+          <t xml:space="preserve">4070</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2229011</t>
+          <t xml:space="preserve">2223675</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J86">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291940</t>
+          <t xml:space="preserve">311292384</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-10</t>
+          <t xml:space="preserve">2028-01-12</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 49</t>
+          <t xml:space="preserve">Ammershøjvej 2</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6501,20 +6501,20 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2223675</t>
+          <t xml:space="preserve">8383897</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J87">
-        <v>188</v>
+        <v>106</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311292384</t>
+          <t xml:space="preserve">311300704</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-12</t>
+          <t xml:space="preserve">2028-03-02</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ammershøjvej 2</t>
+          <t xml:space="preserve">Bramsnæsvigvej 2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">8383897</t>
+          <t xml:space="preserve">2228565</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -6585,11 +6585,11 @@
         </is>
       </c>
       <c r="J88">
-        <v>106</v>
+        <v>165</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311300704</t>
+          <t xml:space="preserve">311300715</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6656,11 +6656,11 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J89">
-        <v>165</v>
+        <v>118</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bramsnæsvigvej 2</t>
+          <t xml:space="preserve">Ejby Strandvej 2B</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6726,20 +6726,20 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228565</t>
+          <t xml:space="preserve">2228222</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J90">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311300715</t>
+          <t xml:space="preserve">311300711</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejby Strandvej 2B</t>
+          <t xml:space="preserve">Hyllebjerget 2</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228222</t>
+          <t xml:space="preserve">2228357</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6810,11 +6810,11 @@
         </is>
       </c>
       <c r="J91">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311300711</t>
+          <t xml:space="preserve">311300717</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyllebjerget 2</t>
+          <t xml:space="preserve">Hyllebjerget 4</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228357</t>
+          <t xml:space="preserve">2228358</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6885,11 +6885,11 @@
         </is>
       </c>
       <c r="J92">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311300717</t>
+          <t xml:space="preserve">311300719</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6941,30 +6941,30 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyllebjerget 4</t>
+          <t xml:space="preserve">Landevejen 75</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070</t>
+          <t xml:space="preserve">4060</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228358</t>
+          <t xml:space="preserve">722482</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J93">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311300719</t>
+          <t xml:space="preserve">311300713</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landevejen 75</t>
+          <t xml:space="preserve">Ærøvej 1</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7026,20 +7026,20 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">722482</t>
+          <t xml:space="preserve">2229031</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J94">
-        <v>137</v>
+        <v>180</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311300713</t>
+          <t xml:space="preserve">311300710</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J95">
@@ -7181,15 +7181,15 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J96">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311300710</t>
+          <t xml:space="preserve">311300714</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ærøvej 1</t>
+          <t xml:space="preserve">Ærøvej 13</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7251,20 +7251,20 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2229031</t>
+          <t xml:space="preserve">2229032</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J97">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311300714</t>
+          <t xml:space="preserve">311300707</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7331,11 +7331,11 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J98">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J99">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J100">
@@ -7556,11 +7556,11 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J101">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -7616,30 +7616,30 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ærøvej 13</t>
+          <t xml:space="preserve">Hornsherredvej 202</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4060</t>
+          <t xml:space="preserve">4070</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2229032</t>
+          <t xml:space="preserve">2225797</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J102">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311300707</t>
+          <t xml:space="preserve">311306918</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-02</t>
+          <t xml:space="preserve">2028-04-06</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7676,12 +7676,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejre Kommune</t>
+          <t xml:space="preserve">RONEKLINT GODS AF 20/10-1998 A/S</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -7691,17 +7691,17 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hornsherredvej 202</t>
+          <t xml:space="preserve">Munkholmvej 409</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070</t>
+          <t xml:space="preserve">4060</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2225797</t>
+          <t xml:space="preserve">722487, 9070172</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -7710,11 +7710,11 @@
         </is>
       </c>
       <c r="J103">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306918</t>
+          <t xml:space="preserve">311306922</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">RONEKLINT GODS AF 20/10-1998 A/S</t>
+          <t xml:space="preserve">Lejre Kommune</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -7766,17 +7766,17 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Munkholmvej 409</t>
+          <t xml:space="preserve">Bispegårdsvej 6</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">4060</t>
+          <t xml:space="preserve">4320</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">722487, 9070172</t>
+          <t xml:space="preserve">8242580</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7785,11 +7785,11 @@
         </is>
       </c>
       <c r="J104">
-        <v>119</v>
+        <v>245</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306922</t>
+          <t xml:space="preserve">311314949</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-06</t>
+          <t xml:space="preserve">2028-05-18</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bispegårdsvej 6</t>
+          <t xml:space="preserve">Engtoften 22</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7851,20 +7851,20 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">8242580</t>
+          <t xml:space="preserve">2226810</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J105">
-        <v>245</v>
+        <v>120</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311314949</t>
+          <t xml:space="preserve">311314950</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7916,30 +7916,30 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engtoften 22</t>
+          <t xml:space="preserve">Hovedvejen 10B</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2226810</t>
+          <t xml:space="preserve">7903255</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J106">
-        <v>120</v>
+        <v>192</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311314950</t>
+          <t xml:space="preserve">311318644</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-18</t>
+          <t xml:space="preserve">2028-06-06</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7991,30 +7991,30 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedvejen 10B</t>
+          <t xml:space="preserve">Flædevadsvej 2</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4320</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">7903255</t>
+          <t xml:space="preserve">2220496</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J107">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311318644</t>
+          <t xml:space="preserve">311319187</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-06</t>
+          <t xml:space="preserve">2028-06-07</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8066,30 +8066,30 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flædevadsvej 2</t>
+          <t xml:space="preserve">Nødager 32</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2220496</t>
+          <t xml:space="preserve">100023432</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J108">
-        <v>212</v>
+        <v>152</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319187</t>
+          <t xml:space="preserve">311319189</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nødager 32</t>
+          <t xml:space="preserve">Nødager 36</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8156,11 +8156,11 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J109">
-        <v>152</v>
+        <v>210</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nødager 36</t>
+          <t xml:space="preserve">Nødager 42</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8231,11 +8231,11 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J110">
-        <v>210</v>
+        <v>152</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nødager 42</t>
+          <t xml:space="preserve">Nødager 46</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8306,11 +8306,11 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J111">
-        <v>152</v>
+        <v>234</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nødager 46</t>
+          <t xml:space="preserve">Nødager 60</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -8381,15 +8381,15 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J112">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319189</t>
+          <t xml:space="preserve">311319188</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8441,40 +8441,40 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nødager 60</t>
+          <t xml:space="preserve">Hyllebjerget 6</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4070</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">100023432</t>
+          <t xml:space="preserve">2228359</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J113">
-        <v>210</v>
+        <v>112</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319188</t>
+          <t xml:space="preserve">311337161</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Boligeftersyn P/S</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-07</t>
+          <t xml:space="preserve">2028-09-20</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyllebjerget 6</t>
+          <t xml:space="preserve">Bygaden 28A</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8526,30 +8526,30 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228359</t>
+          <t xml:space="preserve">2223861</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J114">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311337161</t>
+          <t xml:space="preserve">311612696</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boligeftersyn P/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-20</t>
+          <t xml:space="preserve">2032-07-04</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 28A</t>
+          <t xml:space="preserve">Karlebyvej 130A</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8601,12 +8601,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2223861</t>
+          <t xml:space="preserve">2225368</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J115">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311612696</t>
+          <t xml:space="preserve">311612697</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karlebyvej 130A</t>
+          <t xml:space="preserve">Møllevej 2</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8676,12 +8676,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2225368</t>
+          <t xml:space="preserve">2223859</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J116">
@@ -8689,7 +8689,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311612697</t>
+          <t xml:space="preserve">311612695</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8741,17 +8741,17 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 2</t>
+          <t xml:space="preserve">Klostergårdsvej 5A</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2223859</t>
+          <t xml:space="preserve">2171129</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -8760,21 +8760,21 @@
         </is>
       </c>
       <c r="J117">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311612695</t>
+          <t xml:space="preserve">311739357</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-04</t>
+          <t xml:space="preserve">2034-02-16</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8816,17 +8816,17 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostergårdsvej 5A</t>
+          <t xml:space="preserve">Møllebjergvej 2</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4330</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2171129</t>
+          <t xml:space="preserve">2223212</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -8835,21 +8835,21 @@
         </is>
       </c>
       <c r="J118">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739357</t>
+          <t xml:space="preserve">311751601</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Domutech Solutions A/S</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-16</t>
+          <t xml:space="preserve">2034-04-12</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8891,17 +8891,17 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllebjergvej 2</t>
+          <t xml:space="preserve">Bygaden 35</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">4330</t>
+          <t xml:space="preserve">4070</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2223212</t>
+          <t xml:space="preserve">2224218</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -8910,21 +8910,21 @@
         </is>
       </c>
       <c r="J119">
-        <v>164</v>
+        <v>62</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311751601</t>
+          <t xml:space="preserve">311930045</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech Solutions A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-04-12</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
